--- a/Tareas.xlsx
+++ b/Tareas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorios_github\TFM\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01C5542-1F5A-4656-9429-15FAC39D656B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3040DD77-E490-414E-99E5-4D28202BD394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="975" windowWidth="27345" windowHeight="17205" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>Marcel</t>
   </si>
@@ -166,6 +166,19 @@
   </si>
   <si>
     <t>Nacho/Marcel</t>
+  </si>
+  <si>
+    <t>Reunion
+18/05/2025</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Conclusiones</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -207,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -233,11 +246,20 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -246,9 +268,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -263,13 +282,13 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,19 +304,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:G15" totalsRowShown="0" headerRowDxfId="6" dataDxfId="7">
-  <autoFilter ref="A1:G15" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
-    <sortCondition ref="G1:G15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:H16" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H16" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
+    <sortCondition ref="G1:G16"/>
   </sortState>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="0"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -620,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865E27E8-88FF-4631-B4E1-D37537FD837A}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -629,7 +649,7 @@
     <col min="4" max="4" width="11.42578125" style="5" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" style="5"/>
     <col min="6" max="6" width="4.5703125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="5"/>
+    <col min="7" max="8" width="11.42578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -654,6 +674,9 @@
       <c r="G1" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="H1" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -675,162 +698,187 @@
       <c r="G2" s="6">
         <v>46159</v>
       </c>
+      <c r="H2" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="6">
-        <v>46159</v>
+      <c r="G3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="9">
+        <v>46172</v>
       </c>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="6">
-        <v>46160</v>
-      </c>
-      <c r="I4" s="1"/>
+        <v>46159</v>
+      </c>
+      <c r="H4" s="9">
+        <v>46172</v>
+      </c>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F5" s="7"/>
       <c r="G5" s="6">
-        <v>46164</v>
+        <v>46160</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="7"/>
       <c r="G6" s="6">
-        <v>46167</v>
+        <v>46164</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F7" s="7"/>
       <c r="G7" s="6">
         <v>46167</v>
       </c>
+      <c r="H7" s="9">
+        <v>46167</v>
+      </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="7"/>
       <c r="G8" s="6">
-        <v>46172</v>
+        <v>46167</v>
+      </c>
+      <c r="H8" s="9">
+        <v>46167</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="4">
-        <v>4</v>
-      </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F9" s="7"/>
       <c r="G9" s="6">
-        <v>46173</v>
-      </c>
+        <v>46172</v>
+      </c>
+      <c r="H9" s="9">
+        <v>46172</v>
+      </c>
+      <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D10" s="4">
         <v>3</v>
@@ -840,105 +888,145 @@
       <c r="G10" s="6">
         <v>46173</v>
       </c>
+      <c r="H10" s="9">
+        <v>46173</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="D11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7"/>
       <c r="G11" s="6">
         <v>46173</v>
       </c>
+      <c r="H11" s="9">
+        <v>46167</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>1</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C12" s="4"/>
       <c r="D12" s="4">
-        <v>3</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="7"/>
       <c r="G12" s="6">
-        <v>46178</v>
+        <v>46173</v>
+      </c>
+      <c r="H12" s="9">
+        <v>46173</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4">
-        <v>2</v>
-      </c>
-      <c r="E13" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="6">
-        <v>46183</v>
+        <v>46178</v>
+      </c>
+      <c r="H13" s="9">
+        <v>46178</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D14" s="4">
-        <v>4</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="7"/>
       <c r="G14" s="6">
-        <v>46188</v>
+        <v>46183</v>
+      </c>
+      <c r="H14" s="9">
+        <v>46183</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4">
-        <v>5</v>
-      </c>
-      <c r="E15" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F15" s="7"/>
       <c r="G15" s="6">
+        <v>46188</v>
+      </c>
+      <c r="H15" s="9">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>5</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="6">
         <v>46193</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="H16" s="9">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="17" ht="41.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Tareas.xlsx
+++ b/Tareas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorios_github\TFM\TFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorios_github\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3040DD77-E490-414E-99E5-4D28202BD394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D724E9AD-C38C-4969-A21F-E01E76C6D1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>Marcel</t>
   </si>
@@ -179,6 +179,22 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Reunion
+26/05/26</t>
+  </si>
+  <si>
+    <t>Isa/Marcel</t>
+  </si>
+  <si>
+    <t>Pasar info de la base del Estudio</t>
+  </si>
+  <si>
+    <t>Simplemente selección de archivos</t>
+  </si>
+  <si>
+    <t>Front End</t>
   </si>
 </sst>
 </file>
@@ -220,11 +236,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -253,7 +266,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -304,20 +320,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:H16" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H16" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
-    <sortCondition ref="G1:G16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:I18" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I18" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G18">
+    <sortCondition ref="G1:G18"/>
   </sortState>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="0"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{8B279CE7-51C9-432D-8876-19D3A3878842}" name="Reunion_x000a_26/05/26" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -640,393 +657,485 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865E27E8-88FF-4631-B4E1-D37537FD837A}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
     <col min="2" max="2" width="85.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="5"/>
-    <col min="6" max="6" width="4.5703125" style="8" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="4"/>
+    <col min="6" max="6" width="4.5703125" style="7" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="I1" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="6">
+      <c r="F2" s="6"/>
+      <c r="G2" s="5">
         <v>46159</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="I2" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="9" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>46172</v>
       </c>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="I3" s="8">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="5">
+        <v>46159</v>
+      </c>
+      <c r="H4" s="8">
+        <v>46172</v>
+      </c>
+      <c r="I4" s="8">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="5">
+        <v>46160</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="6">
-        <v>46159</v>
-      </c>
-      <c r="H4" s="9">
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5">
+        <v>46164</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="5">
+        <v>46167</v>
+      </c>
+      <c r="H7" s="8">
+        <v>46167</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="5">
+        <v>46167</v>
+      </c>
+      <c r="H8" s="8">
+        <v>46167</v>
+      </c>
+      <c r="I8" s="8">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="5">
         <v>46172</v>
       </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="H9" s="8">
+        <v>46172</v>
+      </c>
+      <c r="I9" s="8">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="5">
+        <v>46173</v>
+      </c>
+      <c r="H10" s="8">
+        <v>46173</v>
+      </c>
+      <c r="I10" s="8">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="5">
+        <v>46173</v>
+      </c>
+      <c r="H11" s="8">
+        <v>46167</v>
+      </c>
+      <c r="I11" s="5">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
+      <c r="E12" s="3"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="5">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="5">
+        <v>46173</v>
+      </c>
+      <c r="H13" s="8">
+        <v>46173</v>
+      </c>
+      <c r="I13" s="8">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="5">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="D15" s="3">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="6">
-        <v>46160</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="F15" s="6"/>
+      <c r="G15" s="5">
+        <v>46178</v>
+      </c>
+      <c r="H15" s="8">
+        <v>46178</v>
+      </c>
+      <c r="I15" s="8">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D16" s="3">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="5">
+        <v>46183</v>
+      </c>
+      <c r="H16" s="8">
+        <v>46183</v>
+      </c>
+      <c r="I16" s="8">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="6">
-        <v>46164</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="D17" s="3">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="6">
-        <v>46167</v>
-      </c>
-      <c r="H7" s="9">
-        <v>46167</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="6">
-        <v>46167</v>
-      </c>
-      <c r="H8" s="9">
-        <v>46167</v>
-      </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="F17" s="6"/>
+      <c r="G17" s="5">
+        <v>46188</v>
+      </c>
+      <c r="H17" s="8">
+        <v>46188</v>
+      </c>
+      <c r="I17" s="8">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6">
-        <v>46172</v>
-      </c>
-      <c r="H9" s="9">
-        <v>46172</v>
-      </c>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <v>3</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="6">
-        <v>46173</v>
-      </c>
-      <c r="H10" s="9">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="4">
-        <v>3</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="6">
-        <v>46173</v>
-      </c>
-      <c r="H11" s="9">
-        <v>46167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="6">
-        <v>46173</v>
-      </c>
-      <c r="H12" s="9">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4">
-        <v>3</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="6">
-        <v>46178</v>
-      </c>
-      <c r="H13" s="9">
-        <v>46178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="4">
-        <v>2</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="6">
-        <v>46183</v>
-      </c>
-      <c r="H14" s="9">
-        <v>46183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4">
-        <v>4</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="6">
-        <v>46188</v>
-      </c>
-      <c r="H15" s="9">
-        <v>46188</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="D18" s="3">
         <v>5</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4">
-        <v>5</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="6">
+      <c r="E18" s="3"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="5">
         <v>46193</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H18" s="8">
         <v>46193</v>
       </c>
-    </row>
-    <row r="17" ht="41.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="I18" s="8">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Tareas.xlsx
+++ b/Tareas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorios_github\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D724E9AD-C38C-4969-A21F-E01E76C6D1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CFA1A3-63AE-4B46-A502-9D8EA941D069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
+    <workbookView xWindow="11970" yWindow="2145" windowWidth="23745" windowHeight="17340" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/Tareas.xlsx
+++ b/Tareas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorios_github\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CFA1A3-63AE-4B46-A502-9D8EA941D069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE146D8-06D0-4535-911B-8D0F36663077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11970" yWindow="2145" windowWidth="23745" windowHeight="17340" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
   <si>
     <t>Marcel</t>
   </si>
@@ -195,6 +195,13 @@
   </si>
   <si>
     <t>Front End</t>
+  </si>
+  <si>
+    <t>Reunion
+04/06/26</t>
+  </si>
+  <si>
+    <t>done</t>
   </si>
 </sst>
 </file>
@@ -266,7 +273,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -320,21 +330,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:I18" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I18" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:J18" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J18" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G18">
     <sortCondition ref="G1:G18"/>
   </sortState>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{8B279CE7-51C9-432D-8876-19D3A3878842}" name="Reunion_x000a_26/05/26" dataDxfId="0"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{8B279CE7-51C9-432D-8876-19D3A3878842}" name="Reunion_x000a_26/05/26" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{1ED3DD2D-B85A-4B69-9924-8E01CFC3CA08}" name="Reunion_x000a_04/06/26" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -657,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865E27E8-88FF-4631-B4E1-D37537FD837A}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -667,9 +678,10 @@
     <col min="5" max="5" width="11.42578125" style="4"/>
     <col min="6" max="6" width="4.5703125" style="7" customWidth="1"/>
     <col min="7" max="8" width="11.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -697,8 +709,11 @@
       <c r="I1" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -724,8 +739,11 @@
       <c r="I2" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -749,8 +767,11 @@
       <c r="I3" s="8">
         <v>46172</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="5">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -774,8 +795,11 @@
       <c r="I4" s="8">
         <v>46172</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="5">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -801,8 +825,11 @@
       <c r="I5" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -826,8 +853,11 @@
       <c r="I6" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -853,8 +883,11 @@
       <c r="I7" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -878,8 +911,11 @@
       <c r="I8" s="8">
         <v>46178</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="5">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,8 +941,11 @@
       <c r="I9" s="8">
         <v>46178</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="5">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -930,8 +969,11 @@
       <c r="I10" s="8">
         <v>46173</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="5">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -955,8 +997,11 @@
       <c r="I11" s="5">
         <v>46183</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="5">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>48</v>
       </c>
@@ -980,8 +1025,11 @@
       <c r="I12" s="5">
         <v>46171</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1005,8 +1053,11 @@
       <c r="I13" s="8">
         <v>46173</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J13" s="5">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>50</v>
       </c>
@@ -1030,8 +1081,11 @@
       <c r="I14" s="5">
         <v>46183</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="5">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1057,8 +1111,11 @@
       <c r="I15" s="8">
         <v>46178</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J15" s="5">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1082,8 +1139,11 @@
       <c r="I16" s="8">
         <v>46183</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="5">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>35</v>
       </c>
@@ -1109,8 +1169,11 @@
       <c r="I17" s="8">
         <v>46188</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="5">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
@@ -1134,8 +1197,11 @@
       <c r="I18" s="8">
         <v>46193</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="J18" s="5">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Tareas.xlsx
+++ b/Tareas.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorios_github\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE146D8-06D0-4535-911B-8D0F36663077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6725A3E2-5685-4F84-8453-3085B26A8851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tareas" sheetId="1" r:id="rId1"/>
+    <sheet name="DONE" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="59">
   <si>
     <t>Marcel</t>
   </si>
@@ -147,9 +148,6 @@
     <t>capitulo 4, capitulo 6</t>
   </si>
   <si>
-    <t>Redaccion Memoria -Final</t>
-  </si>
-  <si>
     <t>Final Uwu</t>
   </si>
   <si>
@@ -163,9 +161,6 @@
   </si>
   <si>
     <t>Halucination Rate, Dimension/performance rate</t>
-  </si>
-  <si>
-    <t>Nacho/Marcel</t>
   </si>
   <si>
     <t>Reunion
@@ -201,7 +196,32 @@
 04/06/26</t>
   </si>
   <si>
-    <t>done</t>
+    <t>Reunion
+14/06/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacer el indice de la presentacion </t>
+  </si>
+  <si>
+    <t>Preparar los primeros 2minutos de presentacion</t>
+  </si>
+  <si>
+    <t>Corroborar que el cliente del estudio este bien de punta a punta</t>
+  </si>
+  <si>
+    <t>Corroborar que el cliente del banco este bien de punta a punta</t>
+  </si>
+  <si>
+    <t>Crear los usuarios para la presentacion</t>
+  </si>
+  <si>
+    <t>Armar la pagina de presentacion</t>
+  </si>
+  <si>
+    <t>Flujo de trabajo completo</t>
+  </si>
+  <si>
+    <t>Redaccion Memoria - Cambios finales</t>
   </si>
 </sst>
 </file>
@@ -243,13 +263,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -273,7 +290,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="26">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -314,6 +334,53 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -330,22 +397,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:J18" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J18" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G18">
-    <sortCondition ref="G1:G18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:K18" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="A1:K18" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K18">
+    <sortCondition descending="1" ref="C1:C18"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{8B279CE7-51C9-432D-8876-19D3A3878842}" name="Reunion_x000a_26/05/26" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{1ED3DD2D-B85A-4B69-9924-8E01CFC3CA08}" name="Reunion_x000a_04/06/26" dataDxfId="0"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{8B279CE7-51C9-432D-8876-19D3A3878842}" name="Reunion_x000a_26/05/26" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{1ED3DD2D-B85A-4B69-9924-8E01CFC3CA08}" name="Reunion_x000a_04/06/26" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{9758275F-22DC-46D5-A19E-CCBDA9EAFCFC}" name="Reunion_x000a_14/06/26" dataDxfId="13"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4D6E83A8-78A9-409D-8595-A7763FF7A48C}" name="Tabla13" displayName="Tabla13" ref="A1:K16" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K16" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K16">
+    <sortCondition ref="K1:K16"/>
+  </sortState>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{0780FD21-CDAD-4BA4-8339-F56AD6CF9570}" name="Tarea Principal" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{08DBDC13-2E06-4DA6-8B01-14617780ECB2}" name="Descripcion" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{0622E364-D075-4200-A9B3-0C2D067EDCAD}" name="Asignado" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{E49657AD-C804-4850-9487-14997593A4E2}" name="Prioridad" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{7FCDDBC9-9315-410B-8365-282FA3F09ECF}" name="Profesor" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{9AECEF39-D2D0-4DA7-A4B6-4B24A5ACF374}" name="Columna1" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{2BF34B22-4924-4528-A820-AC27A193D478}" name="Reunion_x000a_15/05/26" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{70469407-5C9D-43CF-BEB3-6A0FE3213DFB}" name="Reunion_x000a_18/05/2025" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{4D13D708-AB6D-4D0C-9430-8676FEC98399}" name="Reunion_x000a_26/05/26" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{86B53744-96DC-4D33-A6CD-9A9D7FEF8E45}" name="Reunion_x000a_04/06/26" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{5917D7F0-CB8A-4ADC-886E-1B36D0B9B1F1}" name="Reunion_x000a_14/06/26" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -668,540 +759,955 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865E27E8-88FF-4631-B4E1-D37537FD837A}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
     <col min="2" max="2" width="85.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="4"/>
-    <col min="6" max="6" width="4.5703125" style="7" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="3"/>
+    <col min="6" max="6" width="4.5703125" style="6" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="3" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="4">
+        <v>46159</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46172</v>
+      </c>
+      <c r="I2" s="7">
+        <v>46172</v>
+      </c>
+      <c r="J2" s="4">
+        <v>46210</v>
+      </c>
+      <c r="K2" s="4">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="7">
+        <v>46172</v>
+      </c>
+      <c r="I3" s="7">
+        <v>46172</v>
+      </c>
+      <c r="J3" s="4">
+        <v>46208</v>
+      </c>
+      <c r="K3" s="4">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="4">
+        <v>46183</v>
+      </c>
+      <c r="J4" s="4">
+        <v>46188</v>
+      </c>
+      <c r="K4" s="4">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4">
+        <v>46183</v>
+      </c>
+      <c r="H5" s="7">
+        <v>46183</v>
+      </c>
+      <c r="I5" s="7">
+        <v>46183</v>
+      </c>
+      <c r="J5" s="4">
+        <v>46188</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="4">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="4">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="4">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4">
+        <v>46172</v>
+      </c>
+      <c r="H9" s="7">
+        <v>46172</v>
+      </c>
+      <c r="I9" s="7">
+        <v>46178</v>
+      </c>
+      <c r="J9" s="4">
+        <v>46203</v>
+      </c>
+      <c r="K9" s="4">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4">
+        <v>46193</v>
+      </c>
+      <c r="H10" s="7">
+        <v>46193</v>
+      </c>
+      <c r="I10" s="7">
+        <v>46193</v>
+      </c>
+      <c r="J10" s="4">
+        <v>46203</v>
+      </c>
+      <c r="K10" s="4">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="4">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4">
+        <v>46173</v>
+      </c>
+      <c r="H12" s="7">
+        <v>46173</v>
+      </c>
+      <c r="I12" s="7">
+        <v>46173</v>
+      </c>
+      <c r="J12" s="4">
+        <v>46183</v>
+      </c>
+      <c r="K12" s="4">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="4">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4">
+        <v>46178</v>
+      </c>
+      <c r="H14" s="7">
+        <v>46178</v>
+      </c>
+      <c r="I14" s="7">
+        <v>46178</v>
+      </c>
+      <c r="J14" s="4">
+        <v>46185</v>
+      </c>
+      <c r="K14" s="4">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4">
+        <v>46188</v>
+      </c>
+      <c r="H15" s="7">
+        <v>46188</v>
+      </c>
+      <c r="I15" s="7">
+        <v>46188</v>
+      </c>
+      <c r="J15" s="4">
+        <v>46193</v>
+      </c>
+      <c r="K15" s="4">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="4">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="4">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4564E73F-8625-4762-8983-1175FB3D21C7}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="85.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="3"/>
+    <col min="6" max="6" width="4.5703125" style="6" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="5">
+      <c r="F2" s="5"/>
+      <c r="G2" s="7">
         <v>46159</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4">
+        <v>46160</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4">
+        <v>46164</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="8">
-        <v>46172</v>
-      </c>
-      <c r="I3" s="8">
-        <v>46172</v>
-      </c>
-      <c r="J3" s="5">
-        <v>46208</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="5">
-        <v>46159</v>
-      </c>
-      <c r="H4" s="8">
-        <v>46172</v>
-      </c>
-      <c r="I4" s="8">
-        <v>46172</v>
-      </c>
-      <c r="J4" s="5">
-        <v>46210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4">
+        <v>46167</v>
+      </c>
+      <c r="H5" s="7">
+        <v>46167</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E6" s="2"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="7">
+        <v>46167</v>
+      </c>
+      <c r="H6" s="7">
+        <v>46167</v>
+      </c>
+      <c r="I6" s="4">
+        <v>46178</v>
+      </c>
+      <c r="J6" s="4">
+        <v>46183</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4">
+        <v>46173</v>
+      </c>
+      <c r="H7" s="7">
+        <v>46167</v>
+      </c>
+      <c r="I7" s="7">
+        <v>46183</v>
+      </c>
+      <c r="J7" s="4">
+        <v>46183</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="5">
-        <v>46160</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="7">
+        <v>46171</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="5">
-        <v>46164</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="D9" s="2">
         <v>2</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="5">
-        <v>46167</v>
-      </c>
-      <c r="H7" s="8">
-        <v>46167</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="5">
-        <v>46167</v>
-      </c>
-      <c r="H8" s="8">
-        <v>46167</v>
-      </c>
-      <c r="I8" s="8">
-        <v>46178</v>
-      </c>
-      <c r="J8" s="5">
-        <v>46183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="5">
-        <v>46172</v>
-      </c>
-      <c r="H9" s="8">
-        <v>46172</v>
-      </c>
-      <c r="I9" s="8">
-        <v>46178</v>
-      </c>
-      <c r="J9" s="5">
-        <v>46203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5">
+      <c r="E9" s="2"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4">
         <v>46173</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H9" s="7">
         <v>46173</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I9" s="7">
         <v>46173</v>
       </c>
-      <c r="J10" s="5">
-        <v>46183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="5">
-        <v>46173</v>
-      </c>
-      <c r="H11" s="8">
-        <v>46167</v>
-      </c>
-      <c r="I11" s="5">
-        <v>46183</v>
-      </c>
-      <c r="J11" s="5">
-        <v>46183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="5">
-        <v>46171</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="5">
-        <v>46173</v>
-      </c>
-      <c r="H13" s="8">
-        <v>46173</v>
-      </c>
-      <c r="I13" s="8">
-        <v>46173</v>
-      </c>
-      <c r="J13" s="5">
+      <c r="J9" s="4">
         <v>46188</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="3">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="5">
-        <v>46183</v>
-      </c>
-      <c r="J14" s="5">
-        <v>46188</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5">
-        <v>46178</v>
-      </c>
-      <c r="H15" s="8">
-        <v>46178</v>
-      </c>
-      <c r="I15" s="8">
-        <v>46178</v>
-      </c>
-      <c r="J15" s="5">
-        <v>46185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5">
-        <v>46183</v>
-      </c>
-      <c r="H16" s="8">
-        <v>46183</v>
-      </c>
-      <c r="I16" s="8">
-        <v>46183</v>
-      </c>
-      <c r="J16" s="5">
-        <v>46188</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3">
-        <v>4</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5">
-        <v>46188</v>
-      </c>
-      <c r="H17" s="8">
-        <v>46188</v>
-      </c>
-      <c r="I17" s="8">
-        <v>46188</v>
-      </c>
-      <c r="J17" s="5">
-        <v>46193</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5">
-        <v>46193</v>
-      </c>
-      <c r="H18" s="8">
-        <v>46193</v>
-      </c>
-      <c r="I18" s="8">
-        <v>46193</v>
-      </c>
-      <c r="J18" s="5">
-        <v>46203</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="K9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Tareas.xlsx
+++ b/Tareas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorios_github\TFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6725A3E2-5685-4F84-8453-3085B26A8851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F05C41-D9DB-4F91-A5CB-B12212E40164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
   </bookViews>

--- a/Tareas.xlsx
+++ b/Tareas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorios_github\TFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\OneDrive\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F05C41-D9DB-4F91-A5CB-B12212E40164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2E43D0-19C4-46F1-ABDD-C70D7D0AED78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
+    <workbookView xWindow="-28920" yWindow="2880" windowWidth="29040" windowHeight="15720" xr2:uid="{851AC7AC-0C01-4AA1-B918-0B3E26E4D0FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tareas" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="64">
   <si>
     <t>Marcel</t>
   </si>
@@ -222,16 +220,38 @@
   </si>
   <si>
     <t>Redaccion Memoria - Cambios finales</t>
+  </si>
+  <si>
+    <t>Nacho/Marcel</t>
+  </si>
+  <si>
+    <t>Notas</t>
+  </si>
+  <si>
+    <t>Mirar que podemos insertar en el dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Reunion
+19/06/27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -263,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -286,11 +306,31 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="28">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -336,9 +376,6 @@
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -397,46 +434,48 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:K18" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
-  <autoFilter ref="A1:K18" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}" name="Tabla1" displayName="Tabla1" ref="A1:M18" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A1:M18" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K18">
     <sortCondition descending="1" ref="C1:C18"/>
   </sortState>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{8B279CE7-51C9-432D-8876-19D3A3878842}" name="Reunion_x000a_26/05/26" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{1ED3DD2D-B85A-4B69-9924-8E01CFC3CA08}" name="Reunion_x000a_04/06/26" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{9758275F-22DC-46D5-A19E-CCBDA9EAFCFC}" name="Reunion_x000a_14/06/26" dataDxfId="13"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{589D6F3F-C9C4-48C2-A152-BD2659727C79}" name="Tarea Principal" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{6482FBAC-6B56-4B6B-B068-6C3D45EE5D84}" name="Descripcion" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{37F21341-8E00-41BB-96AC-C8A74C5A5803}" name="Asignado" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{402E759D-82A7-40F9-8C46-D0A9E28AD693}" name="Prioridad" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{BAF9ECD1-B8D1-4253-9212-0CCD4259CB7A}" name="Profesor" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{70DB6CCF-A12F-4453-BF64-CF18C52DE295}" name="Columna1" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{5942CD9E-292C-4439-954F-6249C3117470}" name="Reunion_x000a_15/05/26" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{52D8F1E7-3147-4E9A-AA03-B18F48FABAC5}" name="Reunion_x000a_18/05/2025" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{8B279CE7-51C9-432D-8876-19D3A3878842}" name="Reunion_x000a_26/05/26" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{1ED3DD2D-B85A-4B69-9924-8E01CFC3CA08}" name="Reunion_x000a_04/06/26" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{9758275F-22DC-46D5-A19E-CCBDA9EAFCFC}" name="Reunion_x000a_14/06/26" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{7C178E5F-2658-44F7-A006-F7ED407D464A}" name="Reunion_x000a_19/06/27" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{C5266A8B-9531-4B2D-8174-24C2A82D4404}" name="Notas" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4D6E83A8-78A9-409D-8595-A7763FF7A48C}" name="Tabla13" displayName="Tabla13" ref="A1:K16" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4D6E83A8-78A9-409D-8595-A7763FF7A48C}" name="Tabla13" displayName="Tabla13" ref="A1:K16" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:K16" xr:uid="{B1F80A3B-4E7F-41E9-A313-57DFEF224AD9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K16">
     <sortCondition ref="K1:K16"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{0780FD21-CDAD-4BA4-8339-F56AD6CF9570}" name="Tarea Principal" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{08DBDC13-2E06-4DA6-8B01-14617780ECB2}" name="Descripcion" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{0622E364-D075-4200-A9B3-0C2D067EDCAD}" name="Asignado" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{E49657AD-C804-4850-9487-14997593A4E2}" name="Prioridad" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{7FCDDBC9-9315-410B-8365-282FA3F09ECF}" name="Profesor" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{9AECEF39-D2D0-4DA7-A4B6-4B24A5ACF374}" name="Columna1" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{2BF34B22-4924-4528-A820-AC27A193D478}" name="Reunion_x000a_15/05/26" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{70469407-5C9D-43CF-BEB3-6A0FE3213DFB}" name="Reunion_x000a_18/05/2025" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{4D13D708-AB6D-4D0C-9430-8676FEC98399}" name="Reunion_x000a_26/05/26" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{86B53744-96DC-4D33-A6CD-9A9D7FEF8E45}" name="Reunion_x000a_04/06/26" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{5917D7F0-CB8A-4ADC-886E-1B36D0B9B1F1}" name="Reunion_x000a_14/06/26" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{0780FD21-CDAD-4BA4-8339-F56AD6CF9570}" name="Tarea Principal" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{08DBDC13-2E06-4DA6-8B01-14617780ECB2}" name="Descripcion" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{0622E364-D075-4200-A9B3-0C2D067EDCAD}" name="Asignado" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{E49657AD-C804-4850-9487-14997593A4E2}" name="Prioridad" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7FCDDBC9-9315-410B-8365-282FA3F09ECF}" name="Profesor" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{9AECEF39-D2D0-4DA7-A4B6-4B24A5ACF374}" name="Columna1" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{2BF34B22-4924-4528-A820-AC27A193D478}" name="Reunion_x000a_15/05/26" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{70469407-5C9D-43CF-BEB3-6A0FE3213DFB}" name="Reunion_x000a_18/05/2025" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{4D13D708-AB6D-4D0C-9430-8676FEC98399}" name="Reunion_x000a_26/05/26" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{86B53744-96DC-4D33-A6CD-9A9D7FEF8E45}" name="Reunion_x000a_04/06/26" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{5917D7F0-CB8A-4ADC-886E-1B36D0B9B1F1}" name="Reunion_x000a_14/06/26" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -759,20 +798,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865E27E8-88FF-4631-B4E1-D37537FD837A}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="85.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="3"/>
-    <col min="6" max="6" width="4.5703125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="33.125" customWidth="1"/>
+    <col min="2" max="2" width="85.125" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.375" style="3"/>
+    <col min="6" max="6" width="4.625" style="6" customWidth="1"/>
+    <col min="7" max="8" width="11.375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.25" customWidth="1"/>
+    <col min="13" max="13" width="11" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="32.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -806,8 +846,14 @@
       <c r="K1" s="7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="41.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -837,8 +883,12 @@
       <c r="K2" s="4">
         <v>46210</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="4">
+        <v>46210</v>
+      </c>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" spans="1:13" ht="41.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -868,8 +918,12 @@
       <c r="K3" s="4">
         <v>46208</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L3" s="4">
+        <v>46208</v>
+      </c>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" spans="1:13" ht="41.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>48</v>
       </c>
@@ -877,7 +931,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -899,8 +953,14 @@
       <c r="K4" s="4">
         <v>46203</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L4" s="4">
+        <v>46203</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="41.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -930,8 +990,12 @@
       <c r="K5" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" spans="1:13" ht="41.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -940,7 +1004,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="5"/>
@@ -959,8 +1023,12 @@
       <c r="K6" s="4">
         <v>46203</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="4">
+        <v>46203</v>
+      </c>
+      <c r="M6" s="9"/>
+    </row>
+    <row r="7" spans="1:13" ht="41.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>56</v>
       </c>
@@ -988,8 +1056,12 @@
       <c r="K7" s="4">
         <v>46203</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L7" s="4">
+        <v>46203</v>
+      </c>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" spans="1:13" ht="41.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>57</v>
       </c>
@@ -1017,8 +1089,12 @@
       <c r="K8" s="4">
         <v>46203</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L8" s="4">
+        <v>46203</v>
+      </c>
+      <c r="M8" s="9"/>
+    </row>
+    <row r="9" spans="1:13" ht="41.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1050,8 +1126,12 @@
       <c r="K9" s="4">
         <v>46208</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L9" s="4">
+        <v>46208</v>
+      </c>
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" spans="1:13" ht="40.5" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1081,12 +1161,18 @@
       <c r="K10" s="4">
         <v>46213</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L10" s="4">
+        <v>46208</v>
+      </c>
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" spans="1:13" ht="40.5" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="C11" s="2" t="s">
         <v>0</v>
       </c>
@@ -1110,8 +1196,12 @@
       <c r="K11" s="4">
         <v>46203</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L11" s="4">
+        <v>46203</v>
+      </c>
+      <c r="M11" s="9"/>
+    </row>
+    <row r="12" spans="1:13" ht="40.5" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1141,8 +1231,12 @@
       <c r="K12" s="4">
         <v>46203</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="4">
+        <v>46203</v>
+      </c>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="1:13" ht="40.5" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>51</v>
       </c>
@@ -1170,8 +1264,10 @@
       <c r="K13" s="4">
         <v>46203</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L13" s="4"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="1:13" ht="40.5" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -1203,8 +1299,10 @@
       <c r="K14" s="4">
         <v>46190</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="4"/>
+      <c r="M14" s="9"/>
+    </row>
+    <row r="15" spans="1:13" ht="40.5" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>58</v>
       </c>
@@ -1236,8 +1334,10 @@
       <c r="K15" s="4">
         <v>46193</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="4"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="1:13" ht="40.5" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>52</v>
       </c>
@@ -1263,14 +1363,16 @@
       <c r="K16" s="4">
         <v>46193</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L16" s="4"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="1:13" ht="40.5" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="2" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1290,8 +1392,10 @@
       <c r="K17" s="4">
         <v>46203</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="4"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
@@ -1303,8 +1407,11 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="9"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
@@ -1316,19 +1423,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4564E73F-8625-4762-8983-1175FB3D21C7}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="85.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="3"/>
-    <col min="6" max="6" width="4.5703125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="33.125" customWidth="1"/>
+    <col min="2" max="2" width="85.125" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.375" style="3"/>
+    <col min="6" max="6" width="4.625" style="6" customWidth="1"/>
+    <col min="7" max="8" width="11.375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="32.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1363,7 +1470,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="41.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1396,7 +1503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="41.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1429,7 +1536,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="41.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1460,7 +1567,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="41.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
@@ -1493,7 +1600,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="41.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1524,7 +1631,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="41.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -1555,7 +1662,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="41.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -1586,7 +1693,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="41.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1617,7 +1724,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="40.5" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
@@ -1630,7 +1737,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="40.5" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
@@ -1643,7 +1750,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="40.5" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2"/>
@@ -1656,7 +1763,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="40.5" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
@@ -1669,7 +1776,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="40.5" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="2"/>
@@ -1682,7 +1789,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="40.5" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
@@ -1695,7 +1802,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="40.5" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
